--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
@@ -470,6 +470,11 @@
           <t>241</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -477,6 +482,11 @@
           <t>242</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -484,6 +494,11 @@
           <t>243</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -491,6 +506,11 @@
           <t>244</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A1, 3A2, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -498,6 +518,11 @@
           <t>245</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -505,6 +530,11 @@
           <t>246</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -512,6 +542,11 @@
           <t>247</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2A, 2B, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -519,6 +554,11 @@
           <t>248</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 3, 4, 5A, 5B, 6A, 6B, 7A, 7B, 8A, 8B, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -526,6 +566,11 @@
           <t>249</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 12, 13, 14, 15, 16, 17, 18, 19A, 19B, 20A, 20B, 21A, 21B, 22A, 22B, 23, 2A, 2B, 3, 4, 5, 6A, 6B, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -533,6 +578,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -540,6 +590,11 @@
           <t>251</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 2, 20, 21, 22, 23, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -547,6 +602,11 @@
           <t>252</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -554,6 +614,11 @@
           <t>253</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 4</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -561,6 +626,11 @@
           <t>254</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -568,6 +638,11 @@
           <t>255</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -575,6 +650,11 @@
           <t>256</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -582,6 +662,11 @@
           <t>257</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -589,6 +674,11 @@
           <t>258</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -596,6 +686,11 @@
           <t>259</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -603,6 +698,11 @@
           <t>260</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -610,6 +710,11 @@
           <t>261</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -617,6 +722,11 @@
           <t>262</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -624,6 +734,11 @@
           <t>263</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -631,6 +746,11 @@
           <t>264</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B1, 1B2, 1B3, 1C1A, 1C1B, 1C2, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -638,6 +758,11 @@
           <t>265</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A1, 5A2, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -645,6 +770,11 @@
           <t>266</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 1C, 1D, 2</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -652,6 +782,11 @@
           <t>267</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -659,6 +794,11 @@
           <t>268</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -666,6 +806,11 @@
           <t>269</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -673,6 +818,11 @@
           <t>270</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -680,6 +830,11 @@
           <t>271</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -687,6 +842,11 @@
           <t>272</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -694,6 +854,11 @@
           <t>273</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -701,6 +866,11 @@
           <t>274</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -708,6 +878,11 @@
           <t>275</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -715,6 +890,11 @@
           <t>276</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B, 8C</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -722,6 +902,11 @@
           <t>277</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -729,11 +914,21 @@
           <t>278</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>279</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
@@ -938,6 +938,11 @@
           <t>280</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 4A1, 4A2, 4B, 5A, 5B, 6A, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -945,6 +950,11 @@
           <t>281</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1A1A, 1A2, 1A3, 1B, 2A, 2B, 3A, 3B, 4A1, 4A2, 4A3, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -952,6 +962,11 @@
           <t>282</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -959,6 +974,11 @@
           <t>283</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -966,6 +986,11 @@
           <t>284</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 3, 4, 5A, 5B1, 5B2, 5B3, 6A, 6B1, 6B2, 6B3, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -973,6 +998,11 @@
           <t>285</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -980,6 +1010,11 @@
           <t>286</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -987,6 +1022,11 @@
           <t>287</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -994,6 +1034,11 @@
           <t>288</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1001,6 +1046,11 @@
           <t>289</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1008,6 +1058,11 @@
           <t>290</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2A1, 2A2, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1015,6 +1070,11 @@
           <t>291</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1A, 1B1A, 1B1B, 1B1C, 1B2A, 1B2B, 2, 3A, 3B</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1022,6 +1082,11 @@
           <t>292</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3A, 3B, 3C, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1029,6 +1094,11 @@
           <t>293</t>
         </is>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 1E, 2A1, 2A2, 2B1, 2B2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1036,6 +1106,11 @@
           <t>294</t>
         </is>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 3A1, 3A2, 3B1, 3B2, 3C1, 3C2, 4</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1043,6 +1118,11 @@
           <t>295</t>
         </is>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B, 6, 7A1A1A, 7A1B, 7A1C, 7A2, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1050,6 +1130,11 @@
           <t>296</t>
         </is>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5A1A, 5A1B, 5A2, 5B1A, 5B1B, 5B2, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1057,6 +1142,11 @@
           <t>297</t>
         </is>
       </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1064,6 +1154,11 @@
           <t>298</t>
         </is>
       </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1071,6 +1166,11 @@
           <t>299</t>
         </is>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1078,6 +1178,11 @@
           <t>300</t>
         </is>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1085,6 +1190,11 @@
           <t>301</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 2A, 2B, 2C, 3, 4A, 4B, 4C</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1092,6 +1202,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3, 4A, 4B1A, 4B1B, 4B2, 4B3, 4B4, 5A, 5B, 6A, 6B, 7A, 7B, 7C, 8</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1099,6 +1214,11 @@
           <t>303</t>
         </is>
       </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1106,6 +1226,11 @@
           <t>304</t>
         </is>
       </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 1C, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1113,6 +1238,11 @@
           <t>305</t>
         </is>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1120,6 +1250,11 @@
           <t>306</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1127,6 +1262,11 @@
           <t>307</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 2, 3A, 3B, 3C, 4, 4A, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1134,6 +1274,11 @@
           <t>308</t>
         </is>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1141,6 +1286,11 @@
           <t>309</t>
         </is>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 3</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1148,6 +1298,11 @@
           <t>310</t>
         </is>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2A3, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1155,6 +1310,11 @@
           <t>311</t>
         </is>
       </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1, 10, 11A1, 11A2, 11A3, 11A4, 11A5, 11B1, 11B2, 12, 2A, 2B, 3A, 3B, 4, 5, 6, 7A, 7B, 8A, 8B, 8C1, 8C2, 8D, 9, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1162,6 +1322,11 @@
           <t>312</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1, 10, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1169,6 +1334,11 @@
           <t>313</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A2, 2A3, 2A4, 2B, 2C, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1176,6 +1346,11 @@
           <t>314</t>
         </is>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1, 10, 2A, 2B, 2C, 3, 4, 5, 6A, 6B, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1183,6 +1358,11 @@
           <t>315</t>
         </is>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1190,6 +1370,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1197,6 +1382,11 @@
           <t>317</t>
         </is>
       </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1204,6 +1394,11 @@
           <t>318</t>
         </is>
       </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1A1, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1211,6 +1406,11 @@
           <t>319</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1218,6 +1418,11 @@
           <t>320</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1225,6 +1430,11 @@
           <t>321</t>
         </is>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1B3, 1C1A, 1C1B, 1C2, 2A1, 2A2, 2B1, 2B2, 3A, 3B, 4A1, 4A2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1232,6 +1442,11 @@
           <t>322</t>
         </is>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1239,6 +1454,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1246,6 +1466,11 @@
           <t>324</t>
         </is>
       </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1253,6 +1478,11 @@
           <t>325</t>
         </is>
       </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1260,6 +1490,11 @@
           <t>326</t>
         </is>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1267,6 +1502,11 @@
           <t>327</t>
         </is>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 2A, 2B, 3, 30, 31, 32, 33, 34, 35, 36, 37, 38, 39, 40, 4A1A, 4B1, 5A1, 5A1B1A, 5A1C1A, 5A2, 5B, 5C, 6A1, 6A1B, 6A2, 6B, 6C, 6D, 6E, 6F, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1274,6 +1514,11 @@
           <t>328</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1, 2A1, 2A2, 2B, 2C, 2D, 2E</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1281,6 +1526,11 @@
           <t>329</t>
         </is>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1288,6 +1538,11 @@
           <t>330</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1295,6 +1550,11 @@
           <t>331</t>
         </is>
       </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1302,6 +1562,11 @@
           <t>332</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12A, 12B, 13A, 13B, 14, 15A, 15B1, 15B2, 15C, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1309,6 +1574,11 @@
           <t>333</t>
         </is>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 2, 3A, 3B1, 3B2, 4, 5, 6, 7A, 7B, 8A, 9</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1316,6 +1586,11 @@
           <t>334</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1323,6 +1598,11 @@
           <t>335</t>
         </is>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1, 10A1, 10A2, 10B, 11, 12, 2, 3A1A1A1, 3A1A1B, 3A1B, 3A1C, 3A1D, 3A2, 3A3, 3A4, 3B, 4A, 4B, 5, 6A, 6B, 6C, 6D, 6E, 6F, 7, 8A1, 8A2, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1330,6 +1610,11 @@
           <t>336</t>
         </is>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1337,6 +1622,11 @@
           <t>337</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1344,6 +1634,11 @@
           <t>338</t>
         </is>
       </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 15, 2, 3A, 3B, 3C, 4, 5, 6, 7A, 7B1, 7B2, 7C, 8A1A1A, 8A1A2, 8A1B, 8A1C, 8A1D1, 8A1D2, 8A2A1A1, 8A2A1B, 8A2A2, 8A2B, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1351,6 +1646,11 @@
           <t>339</t>
         </is>
       </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1358,6 +1658,11 @@
           <t>340</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1, 10, 11A, 11B, 11C1, 11C2, 12, 13A, 13B, 13C, 2, 3, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1365,6 +1670,11 @@
           <t>341</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1372,6 +1682,11 @@
           <t>342</t>
         </is>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1379,6 +1694,11 @@
           <t>343</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1386,6 +1706,11 @@
           <t>344</t>
         </is>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1393,6 +1718,11 @@
           <t>345</t>
         </is>
       </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1400,6 +1730,11 @@
           <t>346</t>
         </is>
       </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4A1A, 4A1B, 4A1C, 4A1D, 4A2, 4B, 5</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1407,6 +1742,11 @@
           <t>347</t>
         </is>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1414,6 +1754,11 @@
           <t>348</t>
         </is>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1421,6 +1766,11 @@
           <t>349</t>
         </is>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1428,6 +1778,11 @@
           <t>350</t>
         </is>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1435,6 +1790,11 @@
           <t>351</t>
         </is>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1442,6 +1802,11 @@
           <t>352</t>
         </is>
       </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 3C, 3D, 3E, 4, 5, 6, 7, 8A, 8B, 8C, 8D</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1449,6 +1814,11 @@
           <t>353</t>
         </is>
       </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5, 6A, 6B1, 6B2, 6C, 6D, 6E, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1456,6 +1826,11 @@
           <t>354</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3A, 3B, 3C, 3D, 4A1, 4A2, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1463,6 +1838,11 @@
           <t>355</t>
         </is>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B, 6C, 6D, 6E, 6F, 6G</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1470,6 +1850,11 @@
           <t>356</t>
         </is>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>10, 11, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -1477,6 +1862,11 @@
           <t>357</t>
         </is>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -1484,6 +1874,11 @@
           <t>358</t>
         </is>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -1491,6 +1886,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -1498,6 +1898,11 @@
           <t>360</t>
         </is>
       </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 1E, 1F, 2A, 2B, 2C</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -1505,11 +1910,21 @@
           <t>361</t>
         </is>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
           <t>362</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14, 2A, 2B, 2C, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
@@ -1934,6 +1934,11 @@
           <t>363</t>
         </is>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16A, 16B, 17, 1A, 1B, 2, 3, 4, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -1941,6 +1946,11 @@
           <t>364</t>
         </is>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 1A, 1B, 2, 3, 4, 5, 6, 7, 8A, 8B, 8C, 8D, 8E, 9</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -1948,6 +1958,11 @@
           <t>365</t>
         </is>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 2C, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -1955,6 +1970,11 @@
           <t>366</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -1962,6 +1982,11 @@
           <t>367</t>
         </is>
       </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -1969,6 +1994,11 @@
           <t>368</t>
         </is>
       </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -1976,6 +2006,11 @@
           <t>369</t>
         </is>
       </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -1983,6 +2018,11 @@
           <t>370</t>
         </is>
       </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -1990,6 +2030,11 @@
           <t>371</t>
         </is>
       </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2, 3, 4A, 4B, 5, 6A, 6B, 7A, 7B, 7C</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -1997,6 +2042,11 @@
           <t>372</t>
         </is>
       </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2004,6 +2054,11 @@
           <t>373</t>
         </is>
       </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2011,6 +2066,11 @@
           <t>374</t>
         </is>
       </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5A, 5B, 6A1, 6A2, 6B, 6C, 6D</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2018,6 +2078,11 @@
           <t>375</t>
         </is>
       </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1, 4A2, 4B, 5, 6A1, 6A2, 6A3, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2025,6 +2090,11 @@
           <t>376</t>
         </is>
       </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A1A, 5A1B, 5A2A, 5A2B, 5B, 6A, 6B, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2032,6 +2102,11 @@
           <t>377</t>
         </is>
       </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2039,6 +2114,11 @@
           <t>378</t>
         </is>
       </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2046,6 +2126,11 @@
           <t>379</t>
         </is>
       </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5A, 5B</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2053,6 +2138,11 @@
           <t>380</t>
         </is>
       </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5A, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2060,6 +2150,11 @@
           <t>381</t>
         </is>
       </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5A, 5B, 6, 7A, 7B, 8</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2067,6 +2162,11 @@
           <t>382</t>
         </is>
       </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1B, 1C, 1D, 1E, 2, 3, 4, 5A, 5A2, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2074,6 +2174,11 @@
           <t>383</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3A, 3B1, 3B2, 3C, 3D, 3E, 3F, 3G, 4</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2081,6 +2186,11 @@
           <t>384</t>
         </is>
       </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 1A, 1B, 2, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2088,6 +2198,11 @@
           <t>385</t>
         </is>
       </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 2, 3A, 3B, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2095,6 +2210,11 @@
           <t>386</t>
         </is>
       </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1, 2A1A, 2A1B, 2A2, 2B, 2C, 3, 4A, 4B</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2102,6 +2222,11 @@
           <t>387</t>
         </is>
       </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5A, 5B, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2109,6 +2234,11 @@
           <t>388</t>
         </is>
       </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2116,6 +2246,11 @@
           <t>389</t>
         </is>
       </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2123,6 +2258,11 @@
           <t>390</t>
         </is>
       </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2130,6 +2270,11 @@
           <t>391</t>
         </is>
       </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2137,6 +2282,11 @@
           <t>392</t>
         </is>
       </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2144,6 +2294,11 @@
           <t>393</t>
         </is>
       </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10, 1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2151,6 +2306,11 @@
           <t>394</t>
         </is>
       </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2158,6 +2318,11 @@
           <t>395</t>
         </is>
       </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2165,6 +2330,11 @@
           <t>396</t>
         </is>
       </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2172,6 +2342,11 @@
           <t>397</t>
         </is>
       </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 3, 4, 5A, 5B, 6A, 6B</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2179,6 +2354,11 @@
           <t>398</t>
         </is>
       </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2186,6 +2366,11 @@
           <t>399</t>
         </is>
       </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2193,6 +2378,11 @@
           <t>400</t>
         </is>
       </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C, 2D, 2E, 2F, 2G, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2200,6 +2390,11 @@
           <t>401</t>
         </is>
       </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2207,6 +2402,11 @@
           <t>402</t>
         </is>
       </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2214,6 +2414,11 @@
           <t>403</t>
         </is>
       </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2221,6 +2426,11 @@
           <t>404</t>
         </is>
       </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2228,11 +2438,21 @@
           <t>405</t>
         </is>
       </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
           <t>406</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
@@ -2462,6 +2462,11 @@
           <t>407</t>
         </is>
       </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2469,6 +2474,11 @@
           <t>408</t>
         </is>
       </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2476,6 +2486,11 @@
           <t>409</t>
         </is>
       </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2483,6 +2498,11 @@
           <t>410</t>
         </is>
       </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2490,6 +2510,11 @@
           <t>411</t>
         </is>
       </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2497,6 +2522,11 @@
           <t>412</t>
         </is>
       </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2504,6 +2534,11 @@
           <t>413</t>
         </is>
       </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4A, 4B, 5A, 5B, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2511,6 +2546,11 @@
           <t>414</t>
         </is>
       </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2518,6 +2558,11 @@
           <t>415</t>
         </is>
       </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2525,6 +2570,11 @@
           <t>416</t>
         </is>
       </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2532,6 +2582,11 @@
           <t>417</t>
         </is>
       </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2539,6 +2594,11 @@
           <t>418</t>
         </is>
       </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2546,6 +2606,11 @@
           <t>419</t>
         </is>
       </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2553,6 +2618,11 @@
           <t>420</t>
         </is>
       </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1A1A, 1A1B, 1A2, 1B, 2, 3, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2560,6 +2630,11 @@
           <t>421</t>
         </is>
       </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1, 2, 3A, 3B, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2567,6 +2642,11 @@
           <t>422</t>
         </is>
       </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2574,6 +2654,11 @@
           <t>423</t>
         </is>
       </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2581,6 +2666,11 @@
           <t>424</t>
         </is>
       </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2588,6 +2678,11 @@
           <t>425</t>
         </is>
       </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2595,6 +2690,11 @@
           <t>426</t>
         </is>
       </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2602,6 +2702,11 @@
           <t>427</t>
         </is>
       </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2609,6 +2714,11 @@
           <t>428</t>
         </is>
       </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2, 3, 4, 5, 6, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2616,6 +2726,11 @@
           <t>429</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2623,6 +2738,11 @@
           <t>430</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2630,6 +2750,11 @@
           <t>431</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2637,6 +2762,11 @@
           <t>432</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2644,6 +2774,11 @@
           <t>433</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1A, 1B1, 1B2, 1C, 1D1, 1D2, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -2651,6 +2786,11 @@
           <t>434</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -2658,6 +2798,11 @@
           <t>435</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -2665,6 +2810,11 @@
           <t>436</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -2672,6 +2822,11 @@
           <t>437</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 2, 3, 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -2679,6 +2834,11 @@
           <t>438</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6A1, 6A2, 6B, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -2686,6 +2846,11 @@
           <t>439</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1A1, 1A2, 1A3, 1B, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -2693,6 +2858,11 @@
           <t>440</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A1A, 4A1B, 4A1C, 4A2, 4A3, 4B, 5, 6</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -2700,6 +2870,11 @@
           <t>441</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -2707,6 +2882,11 @@
           <t>442</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1A1, 1A10, 1A11, 1A12, 1A13, 1A14, 1A15, 1A16, 1A17, 1A18, 1A19, 1A2, 1A20, 1A21, 1A22, 1A23, 1A24A1, 1A24B, 1A3, 1A4, 1A5, 1A6, 1A7, 1A8A1, 1A8A2A, 1A8A2B, 1A8B, 1A9A, 1A9B, 1B, 1C, 1D, 2, 3A1, 3A2, 3B, 4, 5, 6, 7</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -2714,6 +2894,11 @@
           <t>443</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -2721,6 +2906,11 @@
           <t>444</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -2728,6 +2918,11 @@
           <t>445</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1A1, 1A2A, 1A2B, 1B, 2, 3A, 3B1, 3B2</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -2735,6 +2930,11 @@
           <t>446</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1, 2A, 2B, 2C1, 2C2A1A, 2C2A2, 2C2B, 2C2C, 2D1, 2D2, 2E1A, 2E1B, 2E2, 2E3, 2F1A, 2F1B, 2F2, 2F3, 2F4A, 2F4B</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -2742,6 +2942,11 @@
           <t>447</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -2749,6 +2954,11 @@
           <t>448</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -2756,6 +2966,11 @@
           <t>449</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -2763,6 +2978,11 @@
           <t>450</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>12, 13, 14, 15, 16, 17, 18, 1A, 2A, 2B1, 2B10, 2B11, 2B12, 2B13, 2B14, 2B15, 2B16, 2B17, 2B18, 2B19, 2B2, 2B20, 2B21, 2B22, 2B23A, 2B24, 2B25A, 2B26, 2B27A1, 2B28A, 2B29A, 2B3, 2B30, 2B4, 2B5, 2B6, 2B7, 2B8, 2B9</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -2770,6 +2990,11 @@
           <t>451</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -2777,6 +3002,11 @@
           <t>452</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -2784,6 +3014,11 @@
           <t>453</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -2791,6 +3026,11 @@
           <t>454</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -2798,11 +3038,21 @@
           <t>455</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
           <t>456</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Puduvoyal_13.333442_80.144042.xlsx
@@ -3062,6 +3062,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
